--- a/config/auto_configs/2016_Hyundai_Kia_Soul EV(PS EV)_81.4kW.xlsx
+++ b/config/auto_configs/2016_Hyundai_Kia_Soul EV(PS EV)_81.4kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KMA_001EA</t>
+          <t>KMA_0022B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KMA_0022B</t>
+          <t>KMA_001EA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -644,6 +644,292 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KMA_00186</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KMA_00216</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BCM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KMA_001ED</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KMA_001F0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KMA_001F2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EPB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KMA_0021D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KMA_001F7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LDC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KMA_00220</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KMA_001D0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KMA_00180</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SJB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KMA_0021B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KMA_001E1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VMCS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KMA_00203</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>00</t>
         </is>
